--- a/downloads/korrigierte_referenz/Weiterbildung_3NF.xlsx
+++ b/downloads/korrigierte_referenz/Weiterbildung_3NF.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="R79b3029ca60548c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="2" r:id="R6da447baaf074149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="3" r:id="R88034f0e2cd94de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="4" r:id="Rc06afc138d60423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="R78a48580b9d84570"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="2" r:id="R89c56e55fe204f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="3" r:id="Rf93afcd3279c4cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="4" r:id="Rb3b5ef4fc1694c35"/>
   </x:sheets>
 </x:workbook>
 </file>
